--- a/events/Birmingham_2022_TWG/Birmingham_2022_TWG_Results.xlsx
+++ b/events/Birmingham_2022_TWG/Birmingham_2022_TWG_Results.xlsx
@@ -805,6 +805,11 @@
           <t>14:17.88</t>
         </is>
       </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>36743</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1264,6 +1269,11 @@
           <t>15:07.22</t>
         </is>
       </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>142950</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2299,6 +2309,11 @@
           <t>14:10.16</t>
         </is>
       </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>36743</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2554,6 +2569,11 @@
           <t>14:39.88</t>
         </is>
       </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>142950</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2614,6 +2634,11 @@
           <t>15:19.17</t>
         </is>
       </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>49744</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3134,6 +3159,11 @@
           <t>1:26:13.25</t>
         </is>
       </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>36743</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3397,6 +3427,11 @@
           <t>1:28:23.03</t>
         </is>
       </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>49744</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3459,6 +3494,11 @@
           <t>1:28:36.29</t>
         </is>
       </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>142950</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4643,6 +4683,11 @@
           <t>16:21.88</t>
         </is>
       </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>71551</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4705,6 +4750,11 @@
           <t>16:30.06</t>
         </is>
       </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>53544</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4901,6 +4951,11 @@
           <t>16:38.32</t>
         </is>
       </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>130683</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -5422,6 +5477,11 @@
           <t>16:25.01</t>
         </is>
       </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>71551</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -6002,6 +6062,11 @@
           <t>16:05.69</t>
         </is>
       </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>53544</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -6122,6 +6187,11 @@
           <t>16:26.35</t>
         </is>
       </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>130683</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -6843,6 +6913,11 @@
           <t>1:37:09.14</t>
         </is>
       </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>53544</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -7034,6 +7109,11 @@
           <t>1:37:43.15</t>
         </is>
       </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>71551</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -7295,6 +7375,11 @@
       <c r="P105" t="inlineStr">
         <is>
           <t>1:41:31.51</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>130683</t>
         </is>
       </c>
     </row>
@@ -7705,7 +7790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8434,6 +8519,138 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>36743</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Eivind</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>VOLD</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>49744</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Joep</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>BAKEL VAN</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>53544</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Anna Margrete</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>SLETSJOEE</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>71551</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>GOMES</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>130683</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Ardis</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>LUDA</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>142950</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Lajos</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>GYOKOS</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
